--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/magallanes.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -816,6 +816,67 @@
         <v>1483.02</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2945-17-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.102.004-K</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>991.4299999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
